--- a/tutorials/data/hp_data_supervised.xlsx
+++ b/tutorials/data/hp_data_supervised.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nova174\PycharmProjects\pandaprosumer_fork\tutorials\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB19004A-6D7C-4D6E-9561-ADE114C5E340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A9A990-7416-42AB-92A0-2BA9D2E7F4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" xr2:uid="{77CC7637-C27F-405C-9868-B6DB6DBBD63C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77CC7637-C27F-405C-9868-B6DB6DBBD63C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -465,6 +465,8 @@
   <dimension ref="A1:E97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="31.7109375" customWidth="1"/>
     <col min="5" max="5" width="26.140625" customWidth="1"/>
   </cols>
@@ -1273,7 +1275,7 @@
         <v>25</v>
       </c>
       <c r="B48">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C48">
         <v>80</v>
@@ -1290,7 +1292,7 @@
         <v>25</v>
       </c>
       <c r="B49">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C49">
         <v>80</v>
@@ -1307,7 +1309,7 @@
         <v>25</v>
       </c>
       <c r="B50">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C50">
         <v>80</v>
@@ -1324,7 +1326,7 @@
         <v>25</v>
       </c>
       <c r="B51">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C51">
         <v>80</v>
@@ -1341,7 +1343,7 @@
         <v>25</v>
       </c>
       <c r="B52">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C52">
         <v>80</v>
@@ -1358,7 +1360,7 @@
         <v>25</v>
       </c>
       <c r="B53">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C53">
         <v>80</v>
@@ -1375,7 +1377,7 @@
         <v>25</v>
       </c>
       <c r="B54">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C54">
         <v>80</v>
@@ -1392,7 +1394,7 @@
         <v>25</v>
       </c>
       <c r="B55">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C55">
         <v>80</v>
@@ -1409,7 +1411,7 @@
         <v>25</v>
       </c>
       <c r="B56">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C56">
         <v>80</v>
@@ -1426,7 +1428,7 @@
         <v>25</v>
       </c>
       <c r="B57">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C57">
         <v>80</v>
@@ -1443,7 +1445,7 @@
         <v>25</v>
       </c>
       <c r="B58">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C58">
         <v>80</v>
@@ -1460,7 +1462,7 @@
         <v>25</v>
       </c>
       <c r="B59">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C59">
         <v>80</v>
@@ -1477,7 +1479,7 @@
         <v>25</v>
       </c>
       <c r="B60">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C60">
         <v>80</v>
@@ -1494,7 +1496,7 @@
         <v>25</v>
       </c>
       <c r="B61">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C61">
         <v>80</v>
@@ -1511,7 +1513,7 @@
         <v>25</v>
       </c>
       <c r="B62">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C62">
         <v>80</v>
@@ -1528,7 +1530,7 @@
         <v>25</v>
       </c>
       <c r="B63">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C63">
         <v>80</v>
@@ -1545,7 +1547,7 @@
         <v>25</v>
       </c>
       <c r="B64">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C64">
         <v>80</v>
@@ -1562,7 +1564,7 @@
         <v>25</v>
       </c>
       <c r="B65">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C65">
         <v>80</v>
@@ -1579,7 +1581,7 @@
         <v>25</v>
       </c>
       <c r="B66">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C66">
         <v>80</v>
@@ -1596,7 +1598,7 @@
         <v>25</v>
       </c>
       <c r="B67">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C67">
         <v>80</v>
@@ -1613,7 +1615,7 @@
         <v>25</v>
       </c>
       <c r="B68">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C68">
         <v>80</v>
@@ -1630,7 +1632,7 @@
         <v>25</v>
       </c>
       <c r="B69">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C69">
         <v>80</v>
@@ -1647,7 +1649,7 @@
         <v>25</v>
       </c>
       <c r="B70">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C70">
         <v>80</v>
@@ -1664,7 +1666,7 @@
         <v>25</v>
       </c>
       <c r="B71">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C71">
         <v>80</v>
@@ -1681,7 +1683,7 @@
         <v>25</v>
       </c>
       <c r="B72">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C72">
         <v>80</v>
@@ -1698,7 +1700,7 @@
         <v>25</v>
       </c>
       <c r="B73">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C73">
         <v>80</v>
@@ -1715,7 +1717,7 @@
         <v>25</v>
       </c>
       <c r="B74">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C74">
         <v>80</v>
@@ -1732,7 +1734,7 @@
         <v>25</v>
       </c>
       <c r="B75">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C75">
         <v>80</v>
@@ -1749,7 +1751,7 @@
         <v>25</v>
       </c>
       <c r="B76">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C76">
         <v>80</v>
@@ -1766,7 +1768,7 @@
         <v>25</v>
       </c>
       <c r="B77">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C77">
         <v>80</v>
@@ -1783,7 +1785,7 @@
         <v>25</v>
       </c>
       <c r="B78">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C78">
         <v>80</v>
@@ -1800,7 +1802,7 @@
         <v>25</v>
       </c>
       <c r="B79">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C79">
         <v>80</v>
@@ -1817,7 +1819,7 @@
         <v>25</v>
       </c>
       <c r="B80">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C80">
         <v>80</v>
@@ -1834,7 +1836,7 @@
         <v>25</v>
       </c>
       <c r="B81">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C81">
         <v>80</v>
@@ -1851,7 +1853,7 @@
         <v>25</v>
       </c>
       <c r="B82">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C82">
         <v>80</v>
@@ -1868,7 +1870,7 @@
         <v>25</v>
       </c>
       <c r="B83">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C83">
         <v>80</v>
@@ -1885,7 +1887,7 @@
         <v>25</v>
       </c>
       <c r="B84">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C84">
         <v>80</v>
@@ -1902,7 +1904,7 @@
         <v>25</v>
       </c>
       <c r="B85">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C85">
         <v>80</v>
@@ -1919,7 +1921,7 @@
         <v>25</v>
       </c>
       <c r="B86">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C86">
         <v>80</v>
@@ -1936,7 +1938,7 @@
         <v>25</v>
       </c>
       <c r="B87">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C87">
         <v>80</v>
@@ -1953,7 +1955,7 @@
         <v>25</v>
       </c>
       <c r="B88">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C88">
         <v>80</v>
@@ -1970,7 +1972,7 @@
         <v>25</v>
       </c>
       <c r="B89">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C89">
         <v>80</v>
@@ -1987,7 +1989,7 @@
         <v>25</v>
       </c>
       <c r="B90">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C90">
         <v>80</v>
@@ -2004,7 +2006,7 @@
         <v>25</v>
       </c>
       <c r="B91">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C91">
         <v>80</v>
@@ -2021,7 +2023,7 @@
         <v>25</v>
       </c>
       <c r="B92">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C92">
         <v>80</v>
@@ -2038,7 +2040,7 @@
         <v>25</v>
       </c>
       <c r="B93">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C93">
         <v>80</v>
@@ -2055,7 +2057,7 @@
         <v>25</v>
       </c>
       <c r="B94">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C94">
         <v>80</v>
@@ -2072,7 +2074,7 @@
         <v>25</v>
       </c>
       <c r="B95">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C95">
         <v>80</v>
@@ -2089,7 +2091,7 @@
         <v>25</v>
       </c>
       <c r="B96">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C96">
         <v>80</v>
@@ -2106,7 +2108,7 @@
         <v>25</v>
       </c>
       <c r="B97">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C97">
         <v>80</v>

--- a/tutorials/data/hp_data_supervised.xlsx
+++ b/tutorials/data/hp_data_supervised.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nova174\PycharmProjects\pandaprosumer_fork\tutorials\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mena138\Projects\SenergyNets\pandaprosumer_os\tutorials\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB19004A-6D7C-4D6E-9561-ADE114C5E340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9E22C4-68CF-41CE-844E-3A601EC7F6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" xr2:uid="{77CC7637-C27F-405C-9868-B6DB6DBBD63C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{77CC7637-C27F-405C-9868-B6DB6DBBD63C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -465,8 +465,10 @@
   <dimension ref="A1:E97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="31.7109375" customWidth="1"/>
-    <col min="5" max="5" width="26.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -500,7 +502,7 @@
         <v>20</v>
       </c>
       <c r="E2">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -517,7 +519,7 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -534,7 +536,7 @@
         <v>20</v>
       </c>
       <c r="E4">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -551,7 +553,7 @@
         <v>20</v>
       </c>
       <c r="E5">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -568,7 +570,7 @@
         <v>20</v>
       </c>
       <c r="E6">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -585,7 +587,7 @@
         <v>20</v>
       </c>
       <c r="E7">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -602,7 +604,7 @@
         <v>20</v>
       </c>
       <c r="E8">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -619,7 +621,7 @@
         <v>20</v>
       </c>
       <c r="E9">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -636,7 +638,7 @@
         <v>20</v>
       </c>
       <c r="E10">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -653,7 +655,7 @@
         <v>20</v>
       </c>
       <c r="E11">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -670,7 +672,7 @@
         <v>20</v>
       </c>
       <c r="E12">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -687,7 +689,7 @@
         <v>20</v>
       </c>
       <c r="E13">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -704,7 +706,7 @@
         <v>20</v>
       </c>
       <c r="E14">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -721,7 +723,7 @@
         <v>20</v>
       </c>
       <c r="E15">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -738,7 +740,7 @@
         <v>20</v>
       </c>
       <c r="E16">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -755,7 +757,7 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -772,7 +774,7 @@
         <v>20</v>
       </c>
       <c r="E18">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -789,7 +791,7 @@
         <v>20</v>
       </c>
       <c r="E19">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -806,7 +808,7 @@
         <v>20</v>
       </c>
       <c r="E20">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -823,7 +825,7 @@
         <v>20</v>
       </c>
       <c r="E21">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -840,7 +842,7 @@
         <v>20</v>
       </c>
       <c r="E22">
-        <v>0.05</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -857,7 +859,7 @@
         <v>20</v>
       </c>
       <c r="E23">
-        <v>0.05</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -874,7 +876,7 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <v>0.05</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -891,7 +893,7 @@
         <v>20</v>
       </c>
       <c r="E25">
-        <v>0.05</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -908,7 +910,7 @@
         <v>20</v>
       </c>
       <c r="E26">
-        <v>0.05</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -925,7 +927,7 @@
         <v>20</v>
       </c>
       <c r="E27">
-        <v>0.4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -942,7 +944,7 @@
         <v>20</v>
       </c>
       <c r="E28">
-        <v>0.4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -959,7 +961,7 @@
         <v>20</v>
       </c>
       <c r="E29">
-        <v>0.4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -976,7 +978,7 @@
         <v>20</v>
       </c>
       <c r="E30">
-        <v>0.4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -993,7 +995,7 @@
         <v>20</v>
       </c>
       <c r="E31">
-        <v>0.4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1010,7 +1012,7 @@
         <v>20</v>
       </c>
       <c r="E32">
-        <v>0.4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1027,7 +1029,7 @@
         <v>20</v>
       </c>
       <c r="E33">
-        <v>0.4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1044,7 +1046,7 @@
         <v>20</v>
       </c>
       <c r="E34">
-        <v>0.4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1061,7 +1063,7 @@
         <v>20</v>
       </c>
       <c r="E35">
-        <v>0.4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1078,7 +1080,7 @@
         <v>20</v>
       </c>
       <c r="E36">
-        <v>0.4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1095,7 +1097,7 @@
         <v>20</v>
       </c>
       <c r="E37">
-        <v>7.0000000000000007E-2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1112,7 +1114,7 @@
         <v>20</v>
       </c>
       <c r="E38">
-        <v>7.0000000000000007E-2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1129,7 +1131,7 @@
         <v>20</v>
       </c>
       <c r="E39">
-        <v>7.0000000000000007E-2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1146,7 +1148,7 @@
         <v>20</v>
       </c>
       <c r="E40">
-        <v>7.0000000000000007E-2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1163,7 +1165,7 @@
         <v>20</v>
       </c>
       <c r="E41">
-        <v>7.0000000000000007E-2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1180,7 +1182,7 @@
         <v>20</v>
       </c>
       <c r="E42">
-        <v>7.0000000000000007E-2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1197,7 +1199,7 @@
         <v>20</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -1214,7 +1216,7 @@
         <v>20</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -1231,7 +1233,7 @@
         <v>20</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -1248,7 +1250,7 @@
         <v>20</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -1265,7 +1267,7 @@
         <v>20</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1282,7 +1284,7 @@
         <v>20</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1299,7 +1301,7 @@
         <v>20</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1316,7 +1318,7 @@
         <v>20</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -1333,7 +1335,7 @@
         <v>20</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -1350,7 +1352,7 @@
         <v>20</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1367,7 +1369,7 @@
         <v>20</v>
       </c>
       <c r="E53">
-        <v>0.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -1384,7 +1386,7 @@
         <v>20</v>
       </c>
       <c r="E54">
-        <v>0.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -1401,7 +1403,7 @@
         <v>20</v>
       </c>
       <c r="E55">
-        <v>0.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -1418,7 +1420,7 @@
         <v>20</v>
       </c>
       <c r="E56">
-        <v>0.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1435,7 +1437,7 @@
         <v>20</v>
       </c>
       <c r="E57">
-        <v>0.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1452,7 +1454,7 @@
         <v>20</v>
       </c>
       <c r="E58">
-        <v>0.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1469,7 +1471,7 @@
         <v>20</v>
       </c>
       <c r="E59">
-        <v>0.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1486,7 +1488,7 @@
         <v>20</v>
       </c>
       <c r="E60">
-        <v>0.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1503,7 +1505,7 @@
         <v>20</v>
       </c>
       <c r="E61">
-        <v>0.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1520,7 +1522,7 @@
         <v>20</v>
       </c>
       <c r="E62">
-        <v>0.4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -1537,7 +1539,7 @@
         <v>20</v>
       </c>
       <c r="E63">
-        <v>0.4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -1554,7 +1556,7 @@
         <v>20</v>
       </c>
       <c r="E64">
-        <v>0.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -1571,7 +1573,7 @@
         <v>20</v>
       </c>
       <c r="E65">
-        <v>0.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -1588,7 +1590,7 @@
         <v>20</v>
       </c>
       <c r="E66">
-        <v>0.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -1605,7 +1607,7 @@
         <v>20</v>
       </c>
       <c r="E67">
-        <v>0.4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -1622,7 +1624,7 @@
         <v>20</v>
       </c>
       <c r="E68">
-        <v>0.4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -1639,7 +1641,7 @@
         <v>20</v>
       </c>
       <c r="E69">
-        <v>0.4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -1656,7 +1658,7 @@
         <v>20</v>
       </c>
       <c r="E70">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -1673,7 +1675,7 @@
         <v>20</v>
       </c>
       <c r="E71">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -1690,7 +1692,7 @@
         <v>20</v>
       </c>
       <c r="E72">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -1707,7 +1709,7 @@
         <v>20</v>
       </c>
       <c r="E73">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -1724,7 +1726,7 @@
         <v>20</v>
       </c>
       <c r="E74">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -1741,7 +1743,7 @@
         <v>20</v>
       </c>
       <c r="E75">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -1758,7 +1760,7 @@
         <v>20</v>
       </c>
       <c r="E76">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -1775,7 +1777,7 @@
         <v>20</v>
       </c>
       <c r="E77">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -1792,7 +1794,7 @@
         <v>20</v>
       </c>
       <c r="E78">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -1809,7 +1811,7 @@
         <v>20</v>
       </c>
       <c r="E79">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -1826,7 +1828,7 @@
         <v>20</v>
       </c>
       <c r="E80">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -1843,7 +1845,7 @@
         <v>20</v>
       </c>
       <c r="E81">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -1860,7 +1862,7 @@
         <v>20</v>
       </c>
       <c r="E82">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -1877,7 +1879,7 @@
         <v>20</v>
       </c>
       <c r="E83">
-        <v>0.01</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -1894,7 +1896,7 @@
         <v>20</v>
       </c>
       <c r="E84">
-        <v>0.2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -1911,7 +1913,7 @@
         <v>20</v>
       </c>
       <c r="E85">
-        <v>0.2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -1928,7 +1930,7 @@
         <v>20</v>
       </c>
       <c r="E86">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -1945,7 +1947,7 @@
         <v>20</v>
       </c>
       <c r="E87">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -1962,7 +1964,7 @@
         <v>20</v>
       </c>
       <c r="E88">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -1979,7 +1981,7 @@
         <v>20</v>
       </c>
       <c r="E89">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -1996,7 +1998,7 @@
         <v>20</v>
       </c>
       <c r="E90">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2013,7 +2015,7 @@
         <v>20</v>
       </c>
       <c r="E91">
-        <v>0.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2030,7 +2032,7 @@
         <v>20</v>
       </c>
       <c r="E92">
-        <v>0.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2047,7 +2049,7 @@
         <v>20</v>
       </c>
       <c r="E93">
-        <v>0.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2064,7 +2066,7 @@
         <v>20</v>
       </c>
       <c r="E94">
-        <v>0.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2081,7 +2083,7 @@
         <v>20</v>
       </c>
       <c r="E95">
-        <v>0.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2098,7 +2100,7 @@
         <v>20</v>
       </c>
       <c r="E96">
-        <v>0.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -2115,7 +2117,7 @@
         <v>20</v>
       </c>
       <c r="E97">
-        <v>0.2</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
